--- a/scripts/excel2json/translations.xlsx
+++ b/scripts/excel2json/translations.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13100"/>
+    <workbookView windowWidth="29840" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
   <si>
     <t>key</t>
   </si>
@@ -102,6 +102,78 @@
   </si>
   <si>
     <t>¡Felicidades! Has ganado &lt;tag&gt;{point}&lt;/tag&gt; puntos.</t>
+  </si>
+  <si>
+    <t>notification.success</t>
+  </si>
+  <si>
+    <t>成功</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Sucesso</t>
+  </si>
+  <si>
+    <t>Éxito</t>
+  </si>
+  <si>
+    <t>notification.info</t>
+  </si>
+  <si>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>Info</t>
+  </si>
+  <si>
+    <t>Informação</t>
+  </si>
+  <si>
+    <t>Información</t>
+  </si>
+  <si>
+    <t>notification.warning</t>
+  </si>
+  <si>
+    <t>警告</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>Aviso</t>
+  </si>
+  <si>
+    <t>Advertencia</t>
+  </si>
+  <si>
+    <t>notification.error</t>
+  </si>
+  <si>
+    <t>错误</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Erro</t>
+  </si>
+  <si>
+    <t>notification.close</t>
+  </si>
+  <si>
+    <t>关闭通知</t>
+  </si>
+  <si>
+    <t>Close notification</t>
+  </si>
+  <si>
+    <t>Fechar notificação</t>
+  </si>
+  <si>
+    <t>Cerrar notificación</t>
   </si>
 </sst>
 </file>
@@ -1257,17 +1329,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.2596153846154" customWidth="1"/>
+    <col min="1" max="1" width="19.8653846153846" customWidth="1"/>
     <col min="2" max="2" width="44.2307692307692" customWidth="1"/>
     <col min="3" max="3" width="54.8076923076923" customWidth="1"/>
     <col min="4" max="4" width="50.6442307692308" customWidth="1"/>
     <col min="5" max="5" width="51.2788461538462" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1291,18 +1363,18 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1319,7 +1391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1336,7 +1408,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1351,6 +1423,91 @@
       </c>
       <c r="E5" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
